--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608620.5858422071</v>
+        <v>608621</v>
       </c>
       <c r="R2" t="n">
-        <v>6753308.642019226</v>
+        <v>6753309</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608620.5858422071</v>
+        <v>608621</v>
       </c>
       <c r="R3" t="n">
-        <v>6753308.642019226</v>
+        <v>6753309</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2008-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91269018</v>
       </c>
       <c r="B2" t="n">
-        <v>98693</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91269009</v>
       </c>
       <c r="B3" t="n">
-        <v>104127</v>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6473-2024 artfynd.xlsx
+++ b/artfynd/A 6473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91269018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91269009</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>